--- a/Accounts_Payable.xlsx
+++ b/Accounts_Payable.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juliana\Desktop\linkedin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juliana\Documents\GitHub\excel-payment-control-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55DCEB01-1C76-4A20-8A0D-E9863726AE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27581045-D677-4FAB-82AF-E5BC25DF96FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1EA73BE3-3350-44EC-86EB-D4284CEBBC60}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId3"/>
+    <pivotCache cacheId="3" r:id="rId3"/>
   </pivotCaches>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
@@ -206,14 +206,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -224,7 +223,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="5">
     <dxf>
       <font>
         <color theme="0"/>
@@ -258,56 +257,6 @@
       <font>
         <color rgb="FFFF6D4B"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -436,6 +385,34 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -469,6 +446,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-EE09-49B2-B94E-597DCEDBFE4D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -484,6 +466,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-EE09-49B2-B94E-597DCEDBFE4D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -1337,7 +1324,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AA270347-206F-4117-9448-98628D557B21}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AA270347-206F-4117-9448-98628D557B21}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -1377,12 +1364,36 @@
   <dataFields count="1">
     <dataField name="Sum of Amount" fld="5" baseField="6" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="3">
     <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -1398,44 +1409,6 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
-</file>
-
-<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{9EC9EB22-EFDF-4FD9-B7CC-6CC793C1E1F0}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="10" unboundColumnsRight="1">
-    <queryTableFields count="9">
-      <queryTableField id="1" name="Invoice_ID" tableColumnId="1"/>
-      <queryTableField id="2" name="Supplier" tableColumnId="2"/>
-      <queryTableField id="3" name="Category" tableColumnId="3"/>
-      <queryTableField id="4" name="Description" tableColumnId="4"/>
-      <queryTableField id="5" name="Due_Date" tableColumnId="5"/>
-      <queryTableField id="6" name="Amount" tableColumnId="6"/>
-      <queryTableField id="7" name="Status" tableColumnId="7"/>
-      <queryTableField id="8" name="Payment_Date" tableColumnId="8"/>
-      <queryTableField id="9" dataBound="0" tableColumnId="9"/>
-    </queryTableFields>
-  </queryTableRefresh>
-</queryTable>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B4236ED8-FA22-45FE-BCE1-D5B4C56B4B3A}" name="tbl_payments_1" displayName="tbl_payments_1" ref="A1:I11" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:I11" xr:uid="{B4236ED8-FA22-45FE-BCE1-D5B4C56B4B3A}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{89CBAD5A-47AD-4F8D-A3A9-FAAAFCCD0949}" uniqueName="1" name="Invoice_ID" queryTableFieldId="1" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{59172226-CCF4-49C2-92D3-895D20389D06}" uniqueName="2" name="Supplier" queryTableFieldId="2" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{1E0CCC98-8EB1-4C76-984F-44FA1E0D3F7B}" uniqueName="3" name="Category" queryTableFieldId="3" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{B74E64EE-82CA-488B-B83C-E2D5BB798AE9}" uniqueName="4" name="Description" queryTableFieldId="4" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{6DAA939B-1731-4144-B4B2-29B9552D4CBE}" uniqueName="5" name="Due_Date" queryTableFieldId="5" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{8118157B-2EE4-43C5-A5DF-D928597D6DF5}" uniqueName="6" name="Amount" queryTableFieldId="6" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{1651DEAE-71FB-462B-B42E-087C9294FB42}" uniqueName="7" name="Status" queryTableFieldId="7" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{B8494BB3-E563-4061-ABCC-30E3A1633E45}" uniqueName="8" name="Payment_Date" queryTableFieldId="8" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{456D6F82-DF4A-4DC1-8980-76A65EAA04E5}" uniqueName="9" name="Overdue_Check" queryTableFieldId="9" dataDxfId="5">
-      <calculatedColumnFormula>IF(AND(G2="Pending",E2&lt;TODAY()),"Overdue","")</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1798,28 +1771,28 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>1001</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>46091</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <v>120</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>46090</v>
       </c>
       <c r="I2" t="str">
@@ -1828,84 +1801,88 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>1002</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>46082</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>80</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5">
+        <v>46088</v>
+      </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3:I6" ca="1" si="0">IF(AND(G3="Pending",E3&lt;TODAY()),"Overdue","")</f>
-        <v>Overdue</v>
+        <v/>
       </c>
     </row>
     <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>1003</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>46099</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>150</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="5"/>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5">
+        <v>46088</v>
+      </c>
       <c r="I4" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(AND(G4="Pending",E4&lt;TODAY()),"Overdue","")</f>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>1004</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>46086</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>200</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>46085</v>
       </c>
       <c r="I5" t="str">
@@ -1914,159 +1891,163 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>1005</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>46106</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>60</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="5"/>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5">
+        <v>46086</v>
+      </c>
       <c r="I6" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>1006</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>46089</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>45</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>46089</v>
       </c>
-      <c r="I7" s="4" t="str">
+      <c r="I7" t="str">
         <f ca="1">IF(AND(G7="Pending",E7&lt;TODAY()),"Overdue","")</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>1007</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>46101</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>320</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="4" t="str">
+      <c r="H8" s="5"/>
+      <c r="I8" t="str">
         <f ca="1">IF(AND(G8="Pending",E8&lt;TODAY()),"Overdue","")</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>1008</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>46083</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>410</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="4" t="str">
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="5">
+        <v>46086</v>
+      </c>
+      <c r="I9" t="str">
         <f ca="1">IF(AND(G9="Pending",E9&lt;TODAY()),"Overdue","")</f>
-        <v>Overdue</v>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>1009</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>46109</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>90</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="4" t="str">
+      <c r="H10" s="5"/>
+      <c r="I10" t="str">
         <f ca="1">IF(AND(G10="Pending",E10&lt;TODAY()),"Overdue","")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>AND(#REF!="Pending",#REF!&lt;TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E14:E1048576">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>AND($G15="Pending",$E15&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1">
-    <cfRule type="expression" dxfId="3" priority="8">
-      <formula>AND(#REF!="Pending",#REF!&lt;TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G1048576 G1:G10">
+  <conditionalFormatting sqref="G1:G10 G12:G1048576">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Pending"</formula>
     </cfRule>
@@ -2074,7 +2055,7 @@
       <formula>"Paid"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I1048576 I1:I10">
+  <conditionalFormatting sqref="I1:I10 I12:I1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Overdue"</formula>
     </cfRule>
@@ -2085,9 +2066,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -2120,7 +2098,7 @@
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>320</v>
       </c>
     </row>
@@ -2128,7 +2106,7 @@
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>290</v>
       </c>
     </row>
@@ -2136,7 +2114,7 @@
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>610</v>
       </c>
     </row>
